--- a/raw_data/CN_results2.xlsx
+++ b/raw_data/CN_results2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lter/Desktop/EA results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lter/Library/Application Support/Box/Box Edit/Documents/1868099659189/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2C9147-CFDC-6549-96DF-2BA779341221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4684DD87-B538-114B-A8A6-A926B1994948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showSheetTabs="0" xWindow="11560" yWindow="1160" windowWidth="26040" windowHeight="17780" xr2:uid="{EB39F799-7925-B840-AC9A-AE51542A5080}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7070" uniqueCount="1802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7502" uniqueCount="1929">
   <si>
     <t>Name001</t>
   </si>
@@ -5438,6 +5438,387 @@
   </si>
   <si>
     <t>duplicate ID, misidentification, burnt sample</t>
+  </si>
+  <si>
+    <t>0012</t>
+  </si>
+  <si>
+    <t>23012026001</t>
+  </si>
+  <si>
+    <t>01/23/2026</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>0670</t>
+  </si>
+  <si>
+    <t>23012026002</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>SYSBPY</t>
+  </si>
+  <si>
+    <t>22012026003</t>
+  </si>
+  <si>
+    <t>01/22/2026</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>23012026003</t>
+  </si>
+  <si>
+    <t>11:51</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>23012026004</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>23012026005</t>
+  </si>
+  <si>
+    <t>1997</t>
+  </si>
+  <si>
+    <t>23012026006</t>
+  </si>
+  <si>
+    <t>12:09</t>
+  </si>
+  <si>
+    <t>655</t>
+  </si>
+  <si>
+    <t>23012026007</t>
+  </si>
+  <si>
+    <t>634</t>
+  </si>
+  <si>
+    <t>23012026008</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>23012026009</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>809</t>
+  </si>
+  <si>
+    <t>23012026010</t>
+  </si>
+  <si>
+    <t>23012026011</t>
+  </si>
+  <si>
+    <t>23012026012</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>594</t>
+  </si>
+  <si>
+    <t>23012026013</t>
+  </si>
+  <si>
+    <t>12:52</t>
+  </si>
+  <si>
+    <t>1186</t>
+  </si>
+  <si>
+    <t>23012026014</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>23012026015</t>
+  </si>
+  <si>
+    <t>608</t>
+  </si>
+  <si>
+    <t>23012026016</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>23012026017</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>632</t>
+  </si>
+  <si>
+    <t>23012026018</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>918</t>
+  </si>
+  <si>
+    <t>23012026019</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>1699</t>
+  </si>
+  <si>
+    <t>23012026020</t>
+  </si>
+  <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>23012026021</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>23012026022</t>
+  </si>
+  <si>
+    <t>13:46</t>
+  </si>
+  <si>
+    <t>23012026023</t>
+  </si>
+  <si>
+    <t>13:52</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>23012026024</t>
+  </si>
+  <si>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>1916</t>
+  </si>
+  <si>
+    <t>23012026025</t>
+  </si>
+  <si>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>23012026026</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>653</t>
+  </si>
+  <si>
+    <t>23012026027</t>
+  </si>
+  <si>
+    <t>14:17</t>
+  </si>
+  <si>
+    <t>538</t>
+  </si>
+  <si>
+    <t>23012026028</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>923</t>
+  </si>
+  <si>
+    <t>23012026029</t>
+  </si>
+  <si>
+    <t>14:29</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>23012026030</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>1488</t>
+  </si>
+  <si>
+    <t>23012026031</t>
+  </si>
+  <si>
+    <t>1894</t>
+  </si>
+  <si>
+    <t>23012026032</t>
+  </si>
+  <si>
+    <t>1476</t>
+  </si>
+  <si>
+    <t>23012026033</t>
+  </si>
+  <si>
+    <t>23012026034</t>
+  </si>
+  <si>
+    <t>23012026035</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>23012026036</t>
+  </si>
+  <si>
+    <t>15:11</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>23012026037</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>23012026038</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>23012026039</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>1509</t>
+  </si>
+  <si>
+    <t>23012026040</t>
+  </si>
+  <si>
+    <t>0533</t>
+  </si>
+  <si>
+    <t>23012026041</t>
+  </si>
+  <si>
+    <t>905</t>
+  </si>
+  <si>
+    <t>23012026042</t>
+  </si>
+  <si>
+    <t>771</t>
+  </si>
+  <si>
+    <t>23012026043</t>
+  </si>
+  <si>
+    <t>23012026044</t>
+  </si>
+  <si>
+    <t>23012026045</t>
+  </si>
+  <si>
+    <t>1355</t>
+  </si>
+  <si>
+    <t>23012026046</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>23012026047</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>23012026048</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>23012026049</t>
+  </si>
+  <si>
+    <t>973</t>
+  </si>
+  <si>
+    <t>23012026050</t>
+  </si>
+  <si>
+    <t>976</t>
+  </si>
+  <si>
+    <t>23012026051</t>
+  </si>
+  <si>
+    <t>23012026052</t>
+  </si>
+  <si>
+    <t>23012026053</t>
   </si>
 </sst>
 </file>
@@ -5811,15 +6192,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7AFC3C-11FA-984B-A11D-B23042D209C4}">
-  <dimension ref="A1:CT954"/>
+  <dimension ref="A1:CT1008"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.796875" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
     <col min="3" max="4" width="20.3984375" style="1" customWidth="1"/>
-    <col min="5" max="6" width="11.796875" style="1"/>
-    <col min="7" max="12" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.796875" style="1"/>
+    <col min="5" max="5" width="11.796875" style="1"/>
+    <col min="6" max="13" width="11.796875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:98" ht="12.75" customHeight="1">
@@ -65882,6 +66263,2484 @@
         <v>1796</v>
       </c>
     </row>
+    <row r="955" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A955" s="2">
+        <v>0</v>
+      </c>
+      <c r="B955" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C955" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D955" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E955" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F955" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G955" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H955" s="2">
+        <v>4.4770000000000003</v>
+      </c>
+      <c r="I955" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J955" s="2">
+        <v>0</v>
+      </c>
+      <c r="K955" s="2"/>
+      <c r="L955" s="2"/>
+      <c r="M955" s="2">
+        <v>1.916960597038269</v>
+      </c>
+      <c r="N955" s="2">
+        <v>41.328739166259766</v>
+      </c>
+      <c r="O955" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="P955" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="956" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A956" s="2">
+        <v>0</v>
+      </c>
+      <c r="B956" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C956" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D956" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E956" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F956" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G956" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H956" s="2">
+        <v>3.6139999999999999</v>
+      </c>
+      <c r="I956" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J956" s="2">
+        <v>0</v>
+      </c>
+      <c r="K956" s="2"/>
+      <c r="L956" s="2"/>
+      <c r="M956" s="2">
+        <v>1.0139827728271484</v>
+      </c>
+      <c r="N956" s="2">
+        <v>48.871196746826172</v>
+      </c>
+      <c r="O956" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="P956" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="957" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A957" s="2">
+        <v>0</v>
+      </c>
+      <c r="B957" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C957" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D957" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E957" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F957" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G957" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H957" s="2"/>
+      <c r="I957" s="2"/>
+      <c r="J957" s="2"/>
+      <c r="K957" s="2"/>
+      <c r="L957" s="2"/>
+      <c r="M957" s="2">
+        <v>0</v>
+      </c>
+      <c r="N957" s="2">
+        <v>0</v>
+      </c>
+      <c r="O957" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="P957" s="1" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="958" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A958" s="2">
+        <v>0</v>
+      </c>
+      <c r="B958" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C958" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D958" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E958" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F958" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="G958" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H958" s="2">
+        <v>4.5810000000000004</v>
+      </c>
+      <c r="I958" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J958" s="2">
+        <v>0</v>
+      </c>
+      <c r="K958" s="2"/>
+      <c r="L958" s="2"/>
+      <c r="M958" s="2">
+        <v>0.6876596212387085</v>
+      </c>
+      <c r="N958" s="2">
+        <v>48.360771179199219</v>
+      </c>
+      <c r="O958" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P958" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="959" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A959" s="2">
+        <v>0</v>
+      </c>
+      <c r="B959" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C959" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D959" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E959" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F959" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="G959" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H959" s="2">
+        <v>4.7679999999999998</v>
+      </c>
+      <c r="I959" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J959" s="2">
+        <v>0</v>
+      </c>
+      <c r="K959" s="2"/>
+      <c r="L959" s="2"/>
+      <c r="M959" s="2">
+        <v>1.3171021938323975</v>
+      </c>
+      <c r="N959" s="2">
+        <v>49.385787963867188</v>
+      </c>
+      <c r="O959" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="P959" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="960" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A960" s="2">
+        <v>0</v>
+      </c>
+      <c r="B960" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C960" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D960" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E960" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F960" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G960" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H960" s="2">
+        <v>4.4969999999999999</v>
+      </c>
+      <c r="I960" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J960" s="2">
+        <v>0</v>
+      </c>
+      <c r="K960" s="2"/>
+      <c r="L960" s="2"/>
+      <c r="M960" s="2">
+        <v>0.85650646686553955</v>
+      </c>
+      <c r="N960" s="2">
+        <v>40.61419677734375</v>
+      </c>
+      <c r="O960" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="P960" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="961" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A961" s="2">
+        <v>0</v>
+      </c>
+      <c r="B961" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C961" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D961" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E961" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F961" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G961" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H961" s="2">
+        <v>3.621</v>
+      </c>
+      <c r="I961" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J961" s="2">
+        <v>0</v>
+      </c>
+      <c r="K961" s="2"/>
+      <c r="L961" s="2"/>
+      <c r="M961" s="2">
+        <v>0.50716888904571533</v>
+      </c>
+      <c r="N961" s="2">
+        <v>50.396198272705078</v>
+      </c>
+      <c r="O961" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="P961" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="962" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A962" s="2">
+        <v>0</v>
+      </c>
+      <c r="B962" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C962" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D962" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E962" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F962" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="G962" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H962" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I962" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J962" s="2">
+        <v>0</v>
+      </c>
+      <c r="K962" s="2"/>
+      <c r="L962" s="2"/>
+      <c r="M962" s="2">
+        <v>0.93227905035018921</v>
+      </c>
+      <c r="N962" s="2">
+        <v>49.490077972412109</v>
+      </c>
+      <c r="O962" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="P962" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="963" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A963" s="2">
+        <v>0</v>
+      </c>
+      <c r="B963" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C963" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D963" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E963" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F963" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G963" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H963" s="2">
+        <v>4.9939999999999998</v>
+      </c>
+      <c r="I963" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J963" s="2">
+        <v>0</v>
+      </c>
+      <c r="K963" s="2"/>
+      <c r="L963" s="2"/>
+      <c r="M963" s="2">
+        <v>0.58594810962677002</v>
+      </c>
+      <c r="N963" s="2">
+        <v>46.690509796142578</v>
+      </c>
+      <c r="O963" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="P963" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="964" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A964" s="2">
+        <v>0</v>
+      </c>
+      <c r="B964" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C964" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D964" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E964" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F964" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G964" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H964" s="2">
+        <v>3.1669999999999998</v>
+      </c>
+      <c r="I964" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J964" s="2">
+        <v>0</v>
+      </c>
+      <c r="K964" s="2"/>
+      <c r="L964" s="2"/>
+      <c r="M964" s="2">
+        <v>1.4040641784667969</v>
+      </c>
+      <c r="N964" s="2">
+        <v>45.622642517089844</v>
+      </c>
+      <c r="O964" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="P964" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="965" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A965" s="2">
+        <v>0</v>
+      </c>
+      <c r="B965" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C965" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D965" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E965" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F965" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="G965" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H965" s="2">
+        <v>4.6029999999999998</v>
+      </c>
+      <c r="I965" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J965" s="2">
+        <v>0</v>
+      </c>
+      <c r="K965" s="2"/>
+      <c r="L965" s="2"/>
+      <c r="M965" s="2">
+        <v>0.59956252574920654</v>
+      </c>
+      <c r="N965" s="2">
+        <v>46.03533935546875</v>
+      </c>
+      <c r="O965" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="P965" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="966" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A966" s="2">
+        <v>0</v>
+      </c>
+      <c r="B966" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C966" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D966" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E966" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F966" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G966" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H966" s="2">
+        <v>3.9129999999999998</v>
+      </c>
+      <c r="I966" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J966" s="2">
+        <v>0</v>
+      </c>
+      <c r="K966" s="2"/>
+      <c r="L966" s="2"/>
+      <c r="M966" s="2">
+        <v>1.3859982490539551</v>
+      </c>
+      <c r="N966" s="2">
+        <v>45.688808441162109</v>
+      </c>
+      <c r="O966" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="P966" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="967" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A967" s="2">
+        <v>0</v>
+      </c>
+      <c r="B967" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C967" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D967" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E967" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F967" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="G967" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H967" s="2">
+        <v>3.2879999999999998</v>
+      </c>
+      <c r="I967" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J967" s="2">
+        <v>0</v>
+      </c>
+      <c r="K967" s="2"/>
+      <c r="L967" s="2"/>
+      <c r="M967" s="2">
+        <v>2.3981161117553711</v>
+      </c>
+      <c r="N967" s="2">
+        <v>44.300617218017578</v>
+      </c>
+      <c r="O967" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="P967" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="968" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A968" s="2">
+        <v>0</v>
+      </c>
+      <c r="B968" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C968" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D968" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E968" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F968" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="G968" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H968" s="2">
+        <v>3.5590000000000002</v>
+      </c>
+      <c r="I968" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J968" s="2">
+        <v>0</v>
+      </c>
+      <c r="K968" s="2"/>
+      <c r="L968" s="2"/>
+      <c r="M968" s="2">
+        <v>0.42953968048095703</v>
+      </c>
+      <c r="N968" s="2">
+        <v>46.627277374267578</v>
+      </c>
+      <c r="O968" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="P968" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="969" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A969" s="2">
+        <v>0</v>
+      </c>
+      <c r="B969" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C969" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D969" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E969" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F969" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="G969" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H969" s="2">
+        <v>3.605</v>
+      </c>
+      <c r="I969" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J969" s="2">
+        <v>0</v>
+      </c>
+      <c r="K969" s="2"/>
+      <c r="L969" s="2"/>
+      <c r="M969" s="2">
+        <v>0.48398286104202271</v>
+      </c>
+      <c r="N969" s="2">
+        <v>47.632427215576172</v>
+      </c>
+      <c r="O969" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="P969" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="970" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A970" s="2">
+        <v>0</v>
+      </c>
+      <c r="B970" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C970" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D970" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E970" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F970" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G970" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H970" s="2">
+        <v>4.3769999999999998</v>
+      </c>
+      <c r="I970" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J970" s="2">
+        <v>0</v>
+      </c>
+      <c r="K970" s="2"/>
+      <c r="L970" s="2"/>
+      <c r="M970" s="2">
+        <v>0.7978217601776123</v>
+      </c>
+      <c r="N970" s="2">
+        <v>48.993141174316406</v>
+      </c>
+      <c r="O970" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="P970" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="971" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A971" s="2">
+        <v>0</v>
+      </c>
+      <c r="B971" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C971" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D971" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E971" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F971" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G971" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H971" s="2">
+        <v>3.4540000000000002</v>
+      </c>
+      <c r="I971" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J971" s="2">
+        <v>0</v>
+      </c>
+      <c r="K971" s="2"/>
+      <c r="L971" s="2"/>
+      <c r="M971" s="2">
+        <v>1.4957021474838257</v>
+      </c>
+      <c r="N971" s="2">
+        <v>40.590255737304688</v>
+      </c>
+      <c r="O971" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="P971" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="972" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A972" s="2">
+        <v>0</v>
+      </c>
+      <c r="B972" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C972" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D972" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E972" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F972" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="G972" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H972" s="2">
+        <v>4.7519999999999998</v>
+      </c>
+      <c r="I972" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J972" s="2">
+        <v>0</v>
+      </c>
+      <c r="K972" s="2"/>
+      <c r="L972" s="2"/>
+      <c r="M972" s="2">
+        <v>1.4745579957962036</v>
+      </c>
+      <c r="N972" s="2">
+        <v>41.43560791015625</v>
+      </c>
+      <c r="O972" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="P972" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="973" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A973" s="2">
+        <v>0</v>
+      </c>
+      <c r="B973" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C973" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D973" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E973" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F973" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G973" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H973" s="2">
+        <v>4.8970000000000002</v>
+      </c>
+      <c r="I973" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J973" s="2">
+        <v>0</v>
+      </c>
+      <c r="K973" s="2"/>
+      <c r="L973" s="2"/>
+      <c r="M973" s="2">
+        <v>0.76566153764724731</v>
+      </c>
+      <c r="N973" s="2">
+        <v>47.239833831787109</v>
+      </c>
+      <c r="O973" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="P973" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="974" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A974" s="2">
+        <v>0</v>
+      </c>
+      <c r="B974" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C974" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D974" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E974" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F974" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G974" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H974" s="2">
+        <v>3.4319999999999999</v>
+      </c>
+      <c r="I974" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J974" s="2">
+        <v>0</v>
+      </c>
+      <c r="K974" s="2"/>
+      <c r="L974" s="2"/>
+      <c r="M974" s="2">
+        <v>1.4481804370880127</v>
+      </c>
+      <c r="N974" s="2">
+        <v>47.631320953369141</v>
+      </c>
+      <c r="O974" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="P974" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="975" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A975" s="2">
+        <v>0</v>
+      </c>
+      <c r="B975" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C975" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D975" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E975" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F975" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="G975" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H975" s="2">
+        <v>4.21</v>
+      </c>
+      <c r="I975" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J975" s="2">
+        <v>0</v>
+      </c>
+      <c r="K975" s="2"/>
+      <c r="L975" s="2"/>
+      <c r="M975" s="2">
+        <v>1.8137792348861694</v>
+      </c>
+      <c r="N975" s="2">
+        <v>44.435329437255859</v>
+      </c>
+      <c r="O975" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="P975" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="976" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A976" s="2">
+        <v>0</v>
+      </c>
+      <c r="B976" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C976" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D976" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E976" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F976" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="G976" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H976" s="2">
+        <v>3.6150000000000002</v>
+      </c>
+      <c r="I976" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J976" s="2">
+        <v>0</v>
+      </c>
+      <c r="K976" s="2"/>
+      <c r="L976" s="2"/>
+      <c r="M976" s="2">
+        <v>0.77358388900756836</v>
+      </c>
+      <c r="N976" s="2">
+        <v>48.915618896484375</v>
+      </c>
+      <c r="O976" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="P976" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="977" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A977" s="2">
+        <v>0</v>
+      </c>
+      <c r="B977" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C977" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D977" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E977" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F977" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="G977" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H977" s="2">
+        <v>3.3250000000000002</v>
+      </c>
+      <c r="I977" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J977" s="2">
+        <v>0</v>
+      </c>
+      <c r="K977" s="2"/>
+      <c r="L977" s="2"/>
+      <c r="M977" s="2">
+        <v>0.40868020057678223</v>
+      </c>
+      <c r="N977" s="2">
+        <v>46.72906494140625</v>
+      </c>
+      <c r="O977" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="P977" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="978" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A978" s="2">
+        <v>0</v>
+      </c>
+      <c r="B978" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C978" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D978" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E978" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F978" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="G978" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H978" s="2">
+        <v>4.2329999999999997</v>
+      </c>
+      <c r="I978" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J978" s="2">
+        <v>0</v>
+      </c>
+      <c r="K978" s="2"/>
+      <c r="L978" s="2"/>
+      <c r="M978" s="2">
+        <v>2.5027117729187012</v>
+      </c>
+      <c r="N978" s="2">
+        <v>44.261131286621094</v>
+      </c>
+      <c r="O978" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="P978" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="979" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A979" s="2">
+        <v>0</v>
+      </c>
+      <c r="B979" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C979" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D979" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E979" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F979" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G979" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H979" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="I979" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J979" s="2">
+        <v>0</v>
+      </c>
+      <c r="K979" s="2"/>
+      <c r="L979" s="2"/>
+      <c r="M979" s="2">
+        <v>0.87921488285064697</v>
+      </c>
+      <c r="N979" s="2">
+        <v>40.770084381103516</v>
+      </c>
+      <c r="O979" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="P979" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="980" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A980" s="2">
+        <v>0</v>
+      </c>
+      <c r="B980" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C980" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D980" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E980" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F980" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G980" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H980" s="2">
+        <v>3.9940000000000002</v>
+      </c>
+      <c r="I980" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J980" s="2">
+        <v>0</v>
+      </c>
+      <c r="K980" s="2"/>
+      <c r="L980" s="2"/>
+      <c r="M980" s="2">
+        <v>1.0465397834777832</v>
+      </c>
+      <c r="N980" s="2">
+        <v>41.331378936767578</v>
+      </c>
+      <c r="O980" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="P980" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="981" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A981" s="2">
+        <v>0</v>
+      </c>
+      <c r="B981" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C981" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D981" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E981" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F981" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G981" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H981" s="2">
+        <v>3.0329999999999999</v>
+      </c>
+      <c r="I981" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J981" s="2">
+        <v>0</v>
+      </c>
+      <c r="K981" s="2"/>
+      <c r="L981" s="2"/>
+      <c r="M981" s="2">
+        <v>0.42711785435676575</v>
+      </c>
+      <c r="N981" s="2">
+        <v>46.763607025146484</v>
+      </c>
+      <c r="O981" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="P981" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="982" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A982" s="2">
+        <v>0</v>
+      </c>
+      <c r="B982" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C982" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D982" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E982" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F982" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G982" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H982" s="2">
+        <v>4.1660000000000004</v>
+      </c>
+      <c r="I982" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J982" s="2">
+        <v>0</v>
+      </c>
+      <c r="K982" s="2"/>
+      <c r="L982" s="2"/>
+      <c r="M982" s="2">
+        <v>1.4717948436737061</v>
+      </c>
+      <c r="N982" s="2">
+        <v>50.628135681152344</v>
+      </c>
+      <c r="O982" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="P982" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="983" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A983" s="2">
+        <v>0</v>
+      </c>
+      <c r="B983" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C983" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D983" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E983" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F983" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="G983" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H983" s="2">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="I983" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J983" s="2">
+        <v>0</v>
+      </c>
+      <c r="K983" s="2"/>
+      <c r="L983" s="2"/>
+      <c r="M983" s="2">
+        <v>0.31263339519500732</v>
+      </c>
+      <c r="N983" s="2">
+        <v>44.27691650390625</v>
+      </c>
+      <c r="O983" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="P983" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="984" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A984" s="2">
+        <v>0</v>
+      </c>
+      <c r="B984" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C984" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D984" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E984" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F984" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G984" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H984" s="2">
+        <v>3.3010000000000002</v>
+      </c>
+      <c r="I984" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J984" s="2">
+        <v>0</v>
+      </c>
+      <c r="K984" s="2"/>
+      <c r="L984" s="2"/>
+      <c r="M984" s="2">
+        <v>1.0743958950042725</v>
+      </c>
+      <c r="N984" s="2">
+        <v>46.661346435546875</v>
+      </c>
+      <c r="O984" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="P984" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="985" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A985" s="2">
+        <v>0</v>
+      </c>
+      <c r="B985" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C985" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D985" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E985" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F985" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="G985" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H985" s="2">
+        <v>3.242</v>
+      </c>
+      <c r="I985" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J985" s="2">
+        <v>0</v>
+      </c>
+      <c r="K985" s="2"/>
+      <c r="L985" s="2"/>
+      <c r="M985" s="2">
+        <v>1.1257342100143433</v>
+      </c>
+      <c r="N985" s="2">
+        <v>46.834774017333984</v>
+      </c>
+      <c r="O985" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="P985" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="986" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A986" s="2">
+        <v>0</v>
+      </c>
+      <c r="B986" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C986" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D986" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E986" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F986" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="G986" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H986" s="2">
+        <v>4.3239999999999998</v>
+      </c>
+      <c r="I986" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J986" s="2">
+        <v>0</v>
+      </c>
+      <c r="K986" s="2"/>
+      <c r="L986" s="2"/>
+      <c r="M986" s="2">
+        <v>0.92325741052627563</v>
+      </c>
+      <c r="N986" s="2">
+        <v>47.360519409179688</v>
+      </c>
+      <c r="O986" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="P986" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="987" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A987" s="2">
+        <v>0</v>
+      </c>
+      <c r="B987" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C987" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D987" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E987" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F987" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="G987" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H987" s="2">
+        <v>3.387</v>
+      </c>
+      <c r="I987" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J987" s="2">
+        <v>0</v>
+      </c>
+      <c r="K987" s="2"/>
+      <c r="L987" s="2"/>
+      <c r="M987" s="2">
+        <v>0.74344450235366821</v>
+      </c>
+      <c r="N987" s="2">
+        <v>52.614372253417969</v>
+      </c>
+      <c r="O987" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="P987" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="988" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A988" s="2">
+        <v>0</v>
+      </c>
+      <c r="B988" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C988" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D988" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E988" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F988" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="G988" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H988" s="2">
+        <v>3.1139999999999999</v>
+      </c>
+      <c r="I988" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J988" s="2">
+        <v>0</v>
+      </c>
+      <c r="K988" s="2"/>
+      <c r="L988" s="2"/>
+      <c r="M988" s="2">
+        <v>1.1454955339431763</v>
+      </c>
+      <c r="N988" s="2">
+        <v>48.378303527832031</v>
+      </c>
+      <c r="O988" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="P988" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="989" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A989" s="2">
+        <v>0</v>
+      </c>
+      <c r="B989" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C989" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D989" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E989" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F989" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G989" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H989" s="2">
+        <v>4.1790000000000003</v>
+      </c>
+      <c r="I989" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J989" s="2">
+        <v>0</v>
+      </c>
+      <c r="K989" s="2"/>
+      <c r="L989" s="2"/>
+      <c r="M989" s="2">
+        <v>0.73441177606582642</v>
+      </c>
+      <c r="N989" s="2">
+        <v>52.515769958496094</v>
+      </c>
+      <c r="O989" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="P989" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="990" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A990" s="2">
+        <v>0</v>
+      </c>
+      <c r="B990" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C990" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D990" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E990" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F990" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G990" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H990" s="2">
+        <v>3.4220000000000002</v>
+      </c>
+      <c r="I990" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J990" s="2">
+        <v>0</v>
+      </c>
+      <c r="K990" s="2"/>
+      <c r="L990" s="2"/>
+      <c r="M990" s="2">
+        <v>2.4556100368499756</v>
+      </c>
+      <c r="N990" s="2">
+        <v>44.482383728027344</v>
+      </c>
+      <c r="O990" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="P990" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="991" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A991" s="2">
+        <v>0</v>
+      </c>
+      <c r="B991" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C991" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D991" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E991" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F991" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="G991" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H991" s="2">
+        <v>3.77</v>
+      </c>
+      <c r="I991" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J991" s="2">
+        <v>0</v>
+      </c>
+      <c r="K991" s="2"/>
+      <c r="L991" s="2"/>
+      <c r="M991" s="2">
+        <v>0.68617427349090576</v>
+      </c>
+      <c r="N991" s="2">
+        <v>43.382926940917969</v>
+      </c>
+      <c r="O991" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="P991" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="992" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A992" s="2">
+        <v>0</v>
+      </c>
+      <c r="B992" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C992" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D992" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E992" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F992" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G992" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H992" s="2">
+        <v>3.831</v>
+      </c>
+      <c r="I992" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J992" s="2">
+        <v>0</v>
+      </c>
+      <c r="K992" s="2"/>
+      <c r="L992" s="2"/>
+      <c r="M992" s="2">
+        <v>1.5269647836685181</v>
+      </c>
+      <c r="N992" s="2">
+        <v>52.630496978759766</v>
+      </c>
+      <c r="O992" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="P992" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="993" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A993" s="2">
+        <v>0</v>
+      </c>
+      <c r="B993" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C993" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D993" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E993" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F993" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G993" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H993" s="2">
+        <v>3.234</v>
+      </c>
+      <c r="I993" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J993" s="2">
+        <v>0</v>
+      </c>
+      <c r="K993" s="2"/>
+      <c r="L993" s="2"/>
+      <c r="M993" s="2">
+        <v>1.3066915273666382</v>
+      </c>
+      <c r="N993" s="2">
+        <v>43.273231506347656</v>
+      </c>
+      <c r="O993" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="P993" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="994" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A994" s="2">
+        <v>0</v>
+      </c>
+      <c r="B994" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C994" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D994" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E994" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F994" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="G994" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H994" s="2">
+        <v>3.3159999999999998</v>
+      </c>
+      <c r="I994" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J994" s="2">
+        <v>0</v>
+      </c>
+      <c r="K994" s="2"/>
+      <c r="L994" s="2"/>
+      <c r="M994" s="2">
+        <v>0.50780892372131348</v>
+      </c>
+      <c r="N994" s="2">
+        <v>46.552623748779297</v>
+      </c>
+      <c r="O994" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="P994" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="995" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A995" s="2">
+        <v>0</v>
+      </c>
+      <c r="B995" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C995" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D995" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E995" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F995" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="G995" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H995" s="2">
+        <v>3.7650000000000001</v>
+      </c>
+      <c r="I995" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J995" s="2">
+        <v>0</v>
+      </c>
+      <c r="K995" s="2"/>
+      <c r="L995" s="2"/>
+      <c r="M995" s="2">
+        <v>1.1623563766479492</v>
+      </c>
+      <c r="N995" s="2">
+        <v>49.498744964599609</v>
+      </c>
+      <c r="O995" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="P995" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="996" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A996" s="2">
+        <v>0</v>
+      </c>
+      <c r="B996" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C996" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D996" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E996" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F996" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="G996" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H996" s="2">
+        <v>3.762</v>
+      </c>
+      <c r="I996" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J996" s="2">
+        <v>0</v>
+      </c>
+      <c r="K996" s="2"/>
+      <c r="L996" s="2"/>
+      <c r="M996" s="2">
+        <v>1.3621832132339478</v>
+      </c>
+      <c r="N996" s="2">
+        <v>47.614963531494141</v>
+      </c>
+      <c r="O996" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="P996" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="997" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A997" s="2">
+        <v>0</v>
+      </c>
+      <c r="B997" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C997" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D997" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E997" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F997" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G997" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H997" s="2">
+        <v>4.9009999999999998</v>
+      </c>
+      <c r="I997" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J997" s="2">
+        <v>0</v>
+      </c>
+      <c r="K997" s="2"/>
+      <c r="L997" s="2"/>
+      <c r="M997" s="2">
+        <v>1.929051399230957</v>
+      </c>
+      <c r="N997" s="2">
+        <v>49.256275177001953</v>
+      </c>
+      <c r="O997" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="P997" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="998" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A998" s="2">
+        <v>0</v>
+      </c>
+      <c r="B998" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C998" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D998" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E998" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F998" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G998" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H998" s="2">
+        <v>3.2959999999999998</v>
+      </c>
+      <c r="I998" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J998" s="2">
+        <v>0</v>
+      </c>
+      <c r="K998" s="2"/>
+      <c r="L998" s="2"/>
+      <c r="M998" s="2">
+        <v>0.41972041130065918</v>
+      </c>
+      <c r="N998" s="2">
+        <v>39.203018188476562</v>
+      </c>
+      <c r="O998" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="P998" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="999" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A999" s="2">
+        <v>0</v>
+      </c>
+      <c r="B999" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C999" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D999" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E999" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F999" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G999" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H999" s="2">
+        <v>4.843</v>
+      </c>
+      <c r="I999" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J999" s="2">
+        <v>0</v>
+      </c>
+      <c r="K999" s="2"/>
+      <c r="L999" s="2"/>
+      <c r="M999" s="2">
+        <v>1.1014676094055176</v>
+      </c>
+      <c r="N999" s="2">
+        <v>50.219364166259766</v>
+      </c>
+      <c r="O999" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="P999" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1000" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1000" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1000" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D1000" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1000" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1000" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="G1000" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1000" s="2">
+        <v>3.7639999999999998</v>
+      </c>
+      <c r="I1000" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1000" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1000" s="2"/>
+      <c r="L1000" s="2"/>
+      <c r="M1000" s="2">
+        <v>2.4790270328521729</v>
+      </c>
+      <c r="N1000" s="2">
+        <v>44.498798370361328</v>
+      </c>
+      <c r="O1000" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="P1000" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1001" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1001" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C1001" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D1001" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1001" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1001" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="G1001" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1001" s="2">
+        <v>4.5869999999999997</v>
+      </c>
+      <c r="I1001" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1001" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1001" s="2"/>
+      <c r="L1001" s="2"/>
+      <c r="M1001" s="2">
+        <v>2.2059059143066406</v>
+      </c>
+      <c r="N1001" s="2">
+        <v>48.344795227050781</v>
+      </c>
+      <c r="O1001" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="P1001" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1002" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1002" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C1002" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D1002" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1002" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1002" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G1002" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1002" s="2">
+        <v>3.0430000000000001</v>
+      </c>
+      <c r="I1002" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1002" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1002" s="2"/>
+      <c r="L1002" s="2"/>
+      <c r="M1002" s="2">
+        <v>0.54390156269073486</v>
+      </c>
+      <c r="N1002" s="2">
+        <v>47.581058502197266</v>
+      </c>
+      <c r="O1002" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="P1002" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1003" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1003" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C1003" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D1003" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1003" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1003" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1003" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1003" s="2">
+        <v>3.5569999999999999</v>
+      </c>
+      <c r="I1003" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1003" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1003" s="2"/>
+      <c r="L1003" s="2"/>
+      <c r="M1003" s="2">
+        <v>0.32631561160087585</v>
+      </c>
+      <c r="N1003" s="2">
+        <v>43.986354827880859</v>
+      </c>
+      <c r="O1003" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="P1003" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1004" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1004" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C1004" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D1004" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1004" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1004" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G1004" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1004" s="2">
+        <v>3.95</v>
+      </c>
+      <c r="I1004" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1004" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1004" s="2"/>
+      <c r="L1004" s="2"/>
+      <c r="M1004" s="2">
+        <v>1.0666991472244263</v>
+      </c>
+      <c r="N1004" s="2">
+        <v>49.126255035400391</v>
+      </c>
+      <c r="O1004" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="P1004" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1005" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1005" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C1005" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D1005" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1005" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1005" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G1005" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1005" s="2">
+        <v>3.4910000000000001</v>
+      </c>
+      <c r="I1005" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1005" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1005" s="2"/>
+      <c r="L1005" s="2"/>
+      <c r="M1005" s="2">
+        <v>0.62597197294235229</v>
+      </c>
+      <c r="N1005" s="2">
+        <v>50.051509857177734</v>
+      </c>
+      <c r="O1005" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="P1005" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1006" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1006" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C1006" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D1006" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1006" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1006" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G1006" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1006" s="2">
+        <v>3.234</v>
+      </c>
+      <c r="I1006" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1006" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1006" s="2"/>
+      <c r="L1006" s="2"/>
+      <c r="M1006" s="2">
+        <v>0.36312860250473022</v>
+      </c>
+      <c r="N1006" s="2">
+        <v>49.139610290527344</v>
+      </c>
+      <c r="O1006" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="P1006" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1007" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1007" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C1007" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1007" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1007" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1007" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G1007" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1007" s="2">
+        <v>4.2839999999999998</v>
+      </c>
+      <c r="I1007" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1007" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1007" s="2"/>
+      <c r="L1007" s="2"/>
+      <c r="M1007" s="2">
+        <v>0.633353590965271</v>
+      </c>
+      <c r="N1007" s="2">
+        <v>50.020187377929688</v>
+      </c>
+      <c r="O1007" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="P1007" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A1008" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1008" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1008" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D1008" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E1008" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F1008" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1008" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1008" s="2">
+        <v>3.5619999999999998</v>
+      </c>
+      <c r="I1008" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J1008" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1008" s="2"/>
+      <c r="L1008" s="2"/>
+      <c r="M1008" s="2">
+        <v>2.5128438472747803</v>
+      </c>
+      <c r="N1008" s="2">
+        <v>44.522712707519531</v>
+      </c>
+      <c r="O1008" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="P1008" s="1" t="s">
+        <v>1796</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions headings="1" gridLines="1"/>

--- a/raw_data/CN_results2.xlsx
+++ b/raw_data/CN_results2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lter/Library/Application Support/Box/Box Edit/Documents/1868099659189/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4684DD87-B538-114B-A8A6-A926B1994948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B418D6B-9FC8-E244-A988-FE568998FFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showSheetTabs="0" xWindow="11560" yWindow="1160" windowWidth="26040" windowHeight="17780" xr2:uid="{EB39F799-7925-B840-AC9A-AE51542A5080}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7502" uniqueCount="1929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7454" uniqueCount="1929">
   <si>
     <t>Name001</t>
   </si>
@@ -5868,7 +5868,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5878,6 +5878,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66302,8 +66305,8 @@
       <c r="N955" s="2">
         <v>41.328739166259766</v>
       </c>
-      <c r="O955" s="2" t="s">
-        <v>1802</v>
+      <c r="O955" s="5">
+        <v>12</v>
       </c>
       <c r="P955" s="1" t="s">
         <v>1796</v>
@@ -66348,8 +66351,8 @@
       <c r="N956" s="2">
         <v>48.871196746826172</v>
       </c>
-      <c r="O956" s="2" t="s">
-        <v>1806</v>
+      <c r="O956" s="5">
+        <v>670</v>
       </c>
       <c r="P956" s="1" t="s">
         <v>1796</v>
@@ -66434,8 +66437,8 @@
       <c r="N958" s="2">
         <v>48.360771179199219</v>
       </c>
-      <c r="O958" s="2" t="s">
-        <v>1813</v>
+      <c r="O958" s="5">
+        <v>1907</v>
       </c>
       <c r="P958" s="1" t="s">
         <v>1796</v>
@@ -66480,8 +66483,8 @@
       <c r="N959" s="2">
         <v>49.385787963867188</v>
       </c>
-      <c r="O959" s="2" t="s">
-        <v>1816</v>
+      <c r="O959" s="5">
+        <v>349</v>
       </c>
       <c r="P959" s="1" t="s">
         <v>1796</v>
@@ -66526,8 +66529,8 @@
       <c r="N960" s="2">
         <v>40.61419677734375</v>
       </c>
-      <c r="O960" s="2" t="s">
-        <v>1818</v>
+      <c r="O960" s="5">
+        <v>1111</v>
       </c>
       <c r="P960" s="1" t="s">
         <v>1796</v>
@@ -66572,8 +66575,8 @@
       <c r="N961" s="2">
         <v>50.396198272705078</v>
       </c>
-      <c r="O961" s="2" t="s">
-        <v>1820</v>
+      <c r="O961" s="5">
+        <v>1997</v>
       </c>
       <c r="P961" s="1" t="s">
         <v>1796</v>
@@ -66618,8 +66621,8 @@
       <c r="N962" s="2">
         <v>49.490077972412109</v>
       </c>
-      <c r="O962" s="2" t="s">
-        <v>1823</v>
+      <c r="O962" s="5">
+        <v>655</v>
       </c>
       <c r="P962" s="1" t="s">
         <v>1796</v>
@@ -66664,8 +66667,8 @@
       <c r="N963" s="2">
         <v>46.690509796142578</v>
       </c>
-      <c r="O963" s="2" t="s">
-        <v>1825</v>
+      <c r="O963" s="5">
+        <v>634</v>
       </c>
       <c r="P963" s="1" t="s">
         <v>1796</v>
@@ -66710,8 +66713,8 @@
       <c r="N964" s="2">
         <v>45.622642517089844</v>
       </c>
-      <c r="O964" s="2" t="s">
-        <v>1827</v>
+      <c r="O964" s="5">
+        <v>1179</v>
       </c>
       <c r="P964" s="1" t="s">
         <v>1796</v>
@@ -66756,8 +66759,8 @@
       <c r="N965" s="2">
         <v>46.03533935546875</v>
       </c>
-      <c r="O965" s="2" t="s">
-        <v>1830</v>
+      <c r="O965" s="5">
+        <v>809</v>
       </c>
       <c r="P965" s="1" t="s">
         <v>1796</v>
@@ -66802,8 +66805,8 @@
       <c r="N966" s="2">
         <v>45.688808441162109</v>
       </c>
-      <c r="O966" s="2" t="s">
-        <v>1827</v>
+      <c r="O966" s="5">
+        <v>1179</v>
       </c>
       <c r="P966" s="1" t="s">
         <v>1796</v>
@@ -66894,8 +66897,8 @@
       <c r="N968" s="2">
         <v>46.627277374267578</v>
       </c>
-      <c r="O968" s="2" t="s">
-        <v>1835</v>
+      <c r="O968" s="5">
+        <v>594</v>
       </c>
       <c r="P968" s="1" t="s">
         <v>1796</v>
@@ -66940,8 +66943,8 @@
       <c r="N969" s="2">
         <v>47.632427215576172</v>
       </c>
-      <c r="O969" s="2" t="s">
-        <v>1838</v>
+      <c r="O969" s="5">
+        <v>1186</v>
       </c>
       <c r="P969" s="1" t="s">
         <v>1796</v>
@@ -66986,8 +66989,8 @@
       <c r="N970" s="2">
         <v>48.993141174316406</v>
       </c>
-      <c r="O970" s="2" t="s">
-        <v>1841</v>
+      <c r="O970" s="5">
+        <v>1083</v>
       </c>
       <c r="P970" s="1" t="s">
         <v>1796</v>
@@ -67032,8 +67035,8 @@
       <c r="N971" s="2">
         <v>40.590255737304688</v>
       </c>
-      <c r="O971" s="2" t="s">
-        <v>1843</v>
+      <c r="O971" s="5">
+        <v>608</v>
       </c>
       <c r="P971" s="1" t="s">
         <v>1796</v>
@@ -67078,8 +67081,8 @@
       <c r="N972" s="2">
         <v>41.43560791015625</v>
       </c>
-      <c r="O972" s="2" t="s">
-        <v>1845</v>
+      <c r="O972" s="5">
+        <v>610</v>
       </c>
       <c r="P972" s="1" t="s">
         <v>1796</v>
@@ -67124,8 +67127,8 @@
       <c r="N973" s="2">
         <v>47.239833831787109</v>
       </c>
-      <c r="O973" s="2" t="s">
-        <v>1848</v>
+      <c r="O973" s="5">
+        <v>632</v>
       </c>
       <c r="P973" s="1" t="s">
         <v>1796</v>
@@ -67170,8 +67173,8 @@
       <c r="N974" s="2">
         <v>47.631320953369141</v>
       </c>
-      <c r="O974" s="2" t="s">
-        <v>1851</v>
+      <c r="O974" s="5">
+        <v>918</v>
       </c>
       <c r="P974" s="1" t="s">
         <v>1796</v>
@@ -67216,8 +67219,8 @@
       <c r="N975" s="2">
         <v>44.435329437255859</v>
       </c>
-      <c r="O975" s="2" t="s">
-        <v>1854</v>
+      <c r="O975" s="5">
+        <v>1699</v>
       </c>
       <c r="P975" s="1" t="s">
         <v>1796</v>
@@ -67262,8 +67265,8 @@
       <c r="N976" s="2">
         <v>48.915618896484375</v>
       </c>
-      <c r="O976" s="2" t="s">
-        <v>1857</v>
+      <c r="O976" s="5">
+        <v>19</v>
       </c>
       <c r="P976" s="1" t="s">
         <v>1796</v>
@@ -67308,8 +67311,8 @@
       <c r="N977" s="2">
         <v>46.72906494140625</v>
       </c>
-      <c r="O977" s="2" t="s">
-        <v>1835</v>
+      <c r="O977" s="5">
+        <v>594</v>
       </c>
       <c r="P977" s="1" t="s">
         <v>1796</v>
@@ -67400,8 +67403,8 @@
       <c r="N979" s="2">
         <v>40.770084381103516</v>
       </c>
-      <c r="O979" s="2" t="s">
-        <v>1864</v>
+      <c r="O979" s="5">
+        <v>99</v>
       </c>
       <c r="P979" s="1" t="s">
         <v>1796</v>
@@ -67446,8 +67449,8 @@
       <c r="N980" s="2">
         <v>41.331378936767578</v>
       </c>
-      <c r="O980" s="2" t="s">
-        <v>1867</v>
+      <c r="O980" s="5">
+        <v>1916</v>
       </c>
       <c r="P980" s="1" t="s">
         <v>1796</v>
@@ -67492,8 +67495,8 @@
       <c r="N981" s="2">
         <v>46.763607025146484</v>
       </c>
-      <c r="O981" s="2" t="s">
-        <v>1870</v>
+      <c r="O981" s="5">
+        <v>267</v>
       </c>
       <c r="P981" s="1" t="s">
         <v>1796</v>
@@ -67538,8 +67541,8 @@
       <c r="N982" s="2">
         <v>50.628135681152344</v>
       </c>
-      <c r="O982" s="2" t="s">
-        <v>1873</v>
+      <c r="O982" s="5">
+        <v>653</v>
       </c>
       <c r="P982" s="1" t="s">
         <v>1796</v>
@@ -67584,8 +67587,8 @@
       <c r="N983" s="2">
         <v>44.27691650390625</v>
       </c>
-      <c r="O983" s="2" t="s">
-        <v>1876</v>
+      <c r="O983" s="5">
+        <v>538</v>
       </c>
       <c r="P983" s="1" t="s">
         <v>1796</v>
@@ -67630,8 +67633,8 @@
       <c r="N984" s="2">
         <v>46.661346435546875</v>
       </c>
-      <c r="O984" s="2" t="s">
-        <v>1879</v>
+      <c r="O984" s="5">
+        <v>923</v>
       </c>
       <c r="P984" s="1" t="s">
         <v>1796</v>
@@ -67676,8 +67679,8 @@
       <c r="N985" s="2">
         <v>46.834774017333984</v>
       </c>
-      <c r="O985" s="2" t="s">
-        <v>1882</v>
+      <c r="O985" s="5">
+        <v>1617</v>
       </c>
       <c r="P985" s="1" t="s">
         <v>1796</v>
@@ -67722,8 +67725,8 @@
       <c r="N986" s="2">
         <v>47.360519409179688</v>
       </c>
-      <c r="O986" s="2" t="s">
-        <v>1885</v>
+      <c r="O986" s="5">
+        <v>1488</v>
       </c>
       <c r="P986" s="1" t="s">
         <v>1796</v>
@@ -67768,8 +67771,8 @@
       <c r="N987" s="2">
         <v>52.614372253417969</v>
       </c>
-      <c r="O987" s="2" t="s">
-        <v>1887</v>
+      <c r="O987" s="5">
+        <v>1894</v>
       </c>
       <c r="P987" s="1" t="s">
         <v>1796</v>
@@ -67814,8 +67817,8 @@
       <c r="N988" s="2">
         <v>48.378303527832031</v>
       </c>
-      <c r="O988" s="2" t="s">
-        <v>1889</v>
+      <c r="O988" s="5">
+        <v>1476</v>
       </c>
       <c r="P988" s="1" t="s">
         <v>1796</v>
@@ -67860,8 +67863,8 @@
       <c r="N989" s="2">
         <v>52.515769958496094</v>
       </c>
-      <c r="O989" s="2" t="s">
-        <v>1887</v>
+      <c r="O989" s="5">
+        <v>1894</v>
       </c>
       <c r="P989" s="1" t="s">
         <v>1796</v>
@@ -67952,8 +67955,8 @@
       <c r="N991" s="2">
         <v>43.382926940917969</v>
       </c>
-      <c r="O991" s="2" t="s">
-        <v>1893</v>
+      <c r="O991" s="5">
+        <v>234</v>
       </c>
       <c r="P991" s="1" t="s">
         <v>1796</v>
@@ -67998,8 +68001,8 @@
       <c r="N992" s="2">
         <v>52.630496978759766</v>
       </c>
-      <c r="O992" s="2" t="s">
-        <v>1896</v>
+      <c r="O992" s="5">
+        <v>392</v>
       </c>
       <c r="P992" s="1" t="s">
         <v>1796</v>
@@ -68044,8 +68047,8 @@
       <c r="N993" s="2">
         <v>43.273231506347656</v>
       </c>
-      <c r="O993" s="2" t="s">
-        <v>1899</v>
+      <c r="O993" s="5">
+        <v>233</v>
       </c>
       <c r="P993" s="1" t="s">
         <v>1796</v>
@@ -68090,8 +68093,8 @@
       <c r="N994" s="2">
         <v>46.552623748779297</v>
       </c>
-      <c r="O994" s="2" t="s">
-        <v>1902</v>
+      <c r="O994" s="5">
+        <v>1085</v>
       </c>
       <c r="P994" s="1" t="s">
         <v>1796</v>
@@ -68136,8 +68139,8 @@
       <c r="N995" s="2">
         <v>49.498744964599609</v>
       </c>
-      <c r="O995" s="2" t="s">
-        <v>1905</v>
+      <c r="O995" s="5">
+        <v>1509</v>
       </c>
       <c r="P995" s="1" t="s">
         <v>1796</v>
@@ -68182,8 +68185,8 @@
       <c r="N996" s="2">
         <v>47.614963531494141</v>
       </c>
-      <c r="O996" s="2" t="s">
-        <v>1907</v>
+      <c r="O996" s="2">
+        <v>533</v>
       </c>
       <c r="P996" s="1" t="s">
         <v>1796</v>
@@ -68228,8 +68231,8 @@
       <c r="N997" s="2">
         <v>49.256275177001953</v>
       </c>
-      <c r="O997" s="2" t="s">
-        <v>1909</v>
+      <c r="O997" s="5">
+        <v>905</v>
       </c>
       <c r="P997" s="1" t="s">
         <v>1796</v>
@@ -68274,8 +68277,8 @@
       <c r="N998" s="2">
         <v>39.203018188476562</v>
       </c>
-      <c r="O998" s="2" t="s">
-        <v>1911</v>
+      <c r="O998" s="5">
+        <v>771</v>
       </c>
       <c r="P998" s="1" t="s">
         <v>1796</v>
@@ -68320,8 +68323,8 @@
       <c r="N999" s="2">
         <v>50.219364166259766</v>
       </c>
-      <c r="O999" s="2" t="s">
-        <v>1905</v>
+      <c r="O999" s="5">
+        <v>1509</v>
       </c>
       <c r="P999" s="1" t="s">
         <v>1796</v>
@@ -68412,8 +68415,8 @@
       <c r="N1001" s="2">
         <v>48.344795227050781</v>
       </c>
-      <c r="O1001" s="2" t="s">
-        <v>1915</v>
+      <c r="O1001" s="5">
+        <v>1355</v>
       </c>
       <c r="P1001" s="1" t="s">
         <v>1796</v>
@@ -68458,8 +68461,8 @@
       <c r="N1002" s="2">
         <v>47.581058502197266</v>
       </c>
-      <c r="O1002" s="2" t="s">
-        <v>1917</v>
+      <c r="O1002" s="5">
+        <v>1600</v>
       </c>
       <c r="P1002" s="1" t="s">
         <v>1796</v>
@@ -68504,8 +68507,8 @@
       <c r="N1003" s="2">
         <v>43.986354827880859</v>
       </c>
-      <c r="O1003" s="2" t="s">
-        <v>1919</v>
+      <c r="O1003" s="5">
+        <v>1042</v>
       </c>
       <c r="P1003" s="1" t="s">
         <v>1796</v>
@@ -68550,8 +68553,8 @@
       <c r="N1004" s="2">
         <v>49.126255035400391</v>
       </c>
-      <c r="O1004" s="2" t="s">
-        <v>1921</v>
+      <c r="O1004" s="5">
+        <v>1028</v>
       </c>
       <c r="P1004" s="1" t="s">
         <v>1796</v>
@@ -68596,8 +68599,8 @@
       <c r="N1005" s="2">
         <v>50.051509857177734</v>
       </c>
-      <c r="O1005" s="2" t="s">
-        <v>1923</v>
+      <c r="O1005" s="5">
+        <v>973</v>
       </c>
       <c r="P1005" s="1" t="s">
         <v>1796</v>
@@ -68642,8 +68645,8 @@
       <c r="N1006" s="2">
         <v>49.139610290527344</v>
       </c>
-      <c r="O1006" s="2" t="s">
-        <v>1925</v>
+      <c r="O1006" s="5">
+        <v>976</v>
       </c>
       <c r="P1006" s="1" t="s">
         <v>1796</v>
@@ -68688,8 +68691,8 @@
       <c r="N1007" s="2">
         <v>50.020187377929688</v>
       </c>
-      <c r="O1007" s="2" t="s">
-        <v>1923</v>
+      <c r="O1007" s="5">
+        <v>973</v>
       </c>
       <c r="P1007" s="1" t="s">
         <v>1796</v>
